--- a/final.xlsx
+++ b/final.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -453,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,17 +457,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AADSD</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>Research, Analysis and Training</t>
         </is>
       </c>
       <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -484,23 +475,17 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>JOB4</t>
+          <t>Snowpro Core</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>JOB1</t>
+          <t>AWS APN</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>JOB2</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>JOB3</t>
+          <t>Snowtrend</t>
         </is>
       </c>
     </row>
@@ -512,7 +497,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Meet</t>
+          <t>Yash Upadhyaya</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -521,16 +506,6 @@
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Meet</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Yash Upadhyaya</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Yash Upadhyaya</t>
         </is>
@@ -539,73 +514,55 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>01-06-2024(Sat)</t>
+          <t>01-07-2024(Mon)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>02-06-2024(Sun)</t>
+          <t>02-07-2024(Tue)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>03-06-2024(Mon)</t>
+          <t>03-07-2024(Wed)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>04-06-2024(Tue)</t>
+          <t>04-07-2024(Thu)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -615,85 +572,61 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>05-06-2024(Wed)</t>
+          <t>05-07-2024(Fri)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>06-06-2024(Thu)</t>
+          <t>06-07-2024(Sat)</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>07-06-2024(Fri)</t>
+          <t>07-07-2024(Sun)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>08-06-2024(Sat)</t>
+          <t>08-07-2024(Mon)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -703,19 +636,13 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>09-06-2024(Sun)</t>
+          <t>09-07-2024(Tue)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -725,107 +652,77 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>10-06-2024(Mon)</t>
+          <t>10-07-2024(Wed)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>11-06-2024(Tue)</t>
+          <t>11-07-2024(Thu)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>12-06-2024(Wed)</t>
+          <t>12-07-2024(Fri)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>13-06-2024(Thu)</t>
+          <t>13-07-2024(Sat)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>14-06-2024(Fri)</t>
+          <t>14-07-2024(Sun)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -835,19 +732,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>15-06-2024(Sat)</t>
+          <t>15-07-2024(Mon)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -857,19 +748,13 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>16-06-2024(Sun)</t>
+          <t>16-07-2024(Tue)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -879,19 +764,13 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>17-06-2024(Mon)</t>
+          <t>17-07-2024(Wed)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -901,19 +780,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>18-06-2024(Tue)</t>
+          <t>18-07-2024(Thu)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -923,19 +796,13 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>19-06-2024(Wed)</t>
+          <t>19-07-2024(Fri)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -945,63 +812,45 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>20-06-2024(Thu)</t>
+          <t>20-07-2024(Sat)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>8</v>
-      </c>
-      <c r="F24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>21-06-2024(Fri)</t>
+          <t>21-07-2024(Sun)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>22-06-2024(Sat)</t>
+          <t>22-07-2024(Mon)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1011,19 +860,13 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>23-06-2024(Sun)</t>
+          <t>23-07-2024(Tue)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1033,41 +876,29 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>24-06-2024(Mon)</t>
+          <t>24-07-2024(Wed)</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>25-06-2024(Tue)</t>
+          <t>25-07-2024(Thu)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1077,41 +908,29 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>26-06-2024(Wed)</t>
+          <t>26-07-2024(Fri)</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>27-06-2024(Thu)</t>
+          <t>27-07-2024(Sat)</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1121,19 +940,13 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>28-06-2024(Fri)</t>
+          <t>28-07-2024(Sun)</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1143,19 +956,13 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>29-06-2024(Sat)</t>
+          <t>29-07-2024(Mon)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1165,19 +972,13 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>30-06-2024(Sun)</t>
+          <t>30-07-2024(Tue)</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1187,19 +988,28 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>31-07-2024(Wed)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="D2:E2"/>
+  <mergeCells count="1">
+    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
